--- a/tables/Smoking_Tier2_Qualitative.xlsx
+++ b/tables/Smoking_Tier2_Qualitative.xlsx
@@ -495,8 +495,10 @@
           <t>Abstinence rate (%)</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>80</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>12/15 (80%)</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -515,7 +517,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>80% abstinence rate at 6 months; single-arm open-label study, no comparator.</t>
+          <t>80% (12/15) biologically verified 7-day point-prevalence smoking abstinence at 6-month follow-up in an open-label, single-arm pilot with no control group, substantially exceeding the &lt;35% typical 6-month abstinence rate for standard smoking-cessation pharmacotherapies/behavioral treatments cited in the article's own Introduction and Discussion.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -523,11 +525,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Johnson 2016</t>
+          <t>Garcia-Romeu 2015</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="C3" t="n">
         <v>15</v>
@@ -542,12 +544,14 @@
           <t>Abstinence rate (%)</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>60</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>12/15 (80%)</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Single-arm abstinence rate; no comparator</t>
+          <t>Predictive analysis (quitters vs non-quitters on SOCQ); not a treatment vs control effect size</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -562,7 +566,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>60% abstinence rate at 30 months; single-arm open-label study, no comparator.</t>
+          <t>80% (12/15) biologically verified 7-day point-prevalence smoking abstinence at 6-month follow-up in an open-label, single-arm design with no control group, well above the &lt;35% 6-month abstinence typical of standard smoking-cessation treatments cited in the article's own Introduction.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -570,11 +574,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Garcia-Romeu 2015</t>
+          <t>Johnson 2016</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C4" t="n">
         <v>15</v>
@@ -586,32 +590,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Group means (quitters vs non-quitters)</t>
+          <t>Abstinence rate (%)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>65.8 vs 52.1</t>
+          <t>9/15 (60%)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Predictive analysis (quitters vs non-quitters on SOCQ); not a treatment vs control effect size</t>
+          <t>Single-arm abstinence rate; no comparator</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>unclassifiable</t>
+          <t>single_arm_positive</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Unclassifiable</t>
+          <t>Positive (Single-arm, no comparator)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Subgroup comparison (quitters vs non-quitters on SOCQ); not a treatment-vs-control effect size.</t>
+          <t>60% (9/15) biologically verified (CO + cotinine + TLFB) smoking abstinence at long-term follow-up (mean 30 months post-TQD, range 16-57 months) in an open-label, single-arm design, contrasted by the authors against &lt;31% typical 12-month abstinence for standard smoking-cessation medications (Discussion).</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
